--- a/outputs/evaluation/CF_M05_req_eval_gt_report.xlsx
+++ b/outputs/evaluation/CF_M05_req_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,18 +507,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2694</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_R07</t>
+          <t>CF_M05_R26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Give or remove access to applications from users.</t>
+          <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -535,53 +535,16 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R_05</t>
+          <t>R_30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The system shall allow users to access applications from the portal.</t>
+          <t>The system must have a secure authentication and permission verification mechanism to ensure each user only accesses authorized information and functionalities.</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3858</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M05_R26</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>59</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>R_30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>The system must have a secure authentication and permission verification mechanism to ensure that each user can only access the information and functionalities that correspond to them.</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.1874</v>
+        <v>0.146</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M05_req_eval_gt_report.xlsx
+++ b/outputs/evaluation/CF_M05_req_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_R05</t>
+          <t>CF_M05_R04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,53 +498,135 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>R_32</t>
+          <t>R_05</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No user can access data from other clients.</t>
+          <t>Access applications from the portal.</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2808</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_R26</t>
+          <t>CF_M05_R09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
+          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CF_M01_R08</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R_30</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication and permission verification mechanism to ensure each user only accesses authorized information and functionalities.</t>
+          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.146</v>
+        <v>0.3294</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M05_R13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Complete and correct translations in both languages.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>53</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CF_M05_R12</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>R_19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>The application must be available in several languages.</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2801</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M05_R24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>R_22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>The learning time for new functionalities should not exceed 5 minutes.</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1506</v>
       </c>
     </row>
   </sheetData>
